--- a/courseware/Labs/Lab-02-FMEA/Worked-Reference.xlsx
+++ b/courseware/Labs/Lab-02-FMEA/Worked-Reference.xlsx
@@ -25491,7 +25491,7 @@
     <t xml:space="preserve">Plot and interpret</t>
   </si>
   <si>
-    <t xml:space="preserve">Create an Excel line chart of delivery_L_h by timestamp for baseline, monitoring and pilot, with the fixed baseline mean/UCL/LCL. Flag points outside the limits without refitting them. Report phase counts and affected IDs. Explain the monitoring shift as a signal requiring investigation, not a proven restriction diagnosis. Keep invalid and missing tests visible in QualityAudit.</t>
+    <t xml:space="preserve">Review the existing Analysis and SPC_Summary chart. Keep the prepared formulas and fixed baseline limits unchanged. Identify valid monitoring points outside the limits and check one example against the source row. Return only three sentences: observed signal, supporting evidence, and an unresolved limitation. Do not rebuild the chart or calculate capability.</t>
   </si>
   <si>
     <t xml:space="preserve">SPC4</t>
@@ -25518,7 +25518,7 @@
     <t xml:space="preserve">Calculate and prioritise</t>
   </si>
   <si>
-    <t xml:space="preserve">Add an Excel formula RPN=S*O*D for every row. Sort a view by RPN descending while preserving mode IDs and source rows. Add a separate high-severity review flag for S&gt;=9. Create an RPN column chart. Do not treat rank or low RPN as evidence of safety acceptance.</t>
+    <t xml:space="preserve">Review the prepared FMEA_Review. Check the RPN formulas for FM01 and FM04, preserving mode IDs and provisional scores. Explain why the severity-9 row still needs review. Return one evidence gap and one proposed action for FM01; keep residual ratings unassessed. Do not rebuild the table or chart.</t>
   </si>
   <si>
     <t xml:space="preserve">FMEA3</t>
@@ -25536,7 +25536,7 @@
     <t xml:space="preserve">Define and measure</t>
   </si>
   <si>
-    <t xml:space="preserve">Use WeeklyEvents, DefectCounts and Evidence. Draft a DMAIC table in Excel: phase, claim, metric, source, limitation, next action. Define the CTQ as delivery-test acceptance deviation, not chemical compliance. Calculate baseline and pilot rates using summed deviations divided by summed opportunities, not a simple average when denominators differ.</t>
+    <t xml:space="preserve">Review the prepared Rate_Comparison, WeeklyEvents and DMAIC tables. Check baseline and pilot rates using summed deviations divided by summed opportunities. Return three cells: measured change, limitation and next evidence. Do not create a full report or a new chart, and do not claim a causal effect from the short pilot.</t>
   </si>
   <si>
     <t xml:space="preserve">DMAIC2</t>

--- a/courseware/Labs/Lab-02-FMEA/Worked-Reference.xlsx
+++ b/courseware/Labs/Lab-02-FMEA/Worked-Reference.xlsx
@@ -24228,7 +24228,7 @@
     <t xml:space="preserve">How to use</t>
   </si>
   <si>
-    <t xml:space="preserve">Save a working copy of Starter.xlsx to your approved OneDrive or SharePoint location. Open it in Excel with your work/school account and use the Copilot side pane. Select the named table before prompting. If Copilot cannot edit, request the formula and insert it manually; record the fallback. Confirm tenant entitlement and supported workbook format before class. Keep the local raw files unchanged.</t>
+    <t xml:space="preserve">For the class, save a working copy of Worked-Reference.xlsx to approved OneDrive or SharePoint storage. Starter.xlsx is optional after-class practice. Open it in Excel with your work/school account and use the Copilot side pane. Select the named table before prompting. If Copilot cannot edit, request the formula and insert it manually; record the fallback. Confirm tenant entitlement and supported workbook format before class. Keep the local raw files unchanged.</t>
   </si>
   <si>
     <t xml:space="preserve">Workbook prompts</t>

--- a/courseware/Labs/Lab-02-FMEA/Worked-Reference.xlsx
+++ b/courseware/Labs/Lab-02-FMEA/Worked-Reference.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="74">
   <si>
     <t xml:space="preserve">Lab 2 - Use Copilot in Excel to create an FMEA review</t>
   </si>
@@ -194,6 +194,36 @@
   </si>
   <si>
     <t xml:space="preserve">Four preserved failure modes, formula-based RPN values, a ranked priority, a severity flag, and evidence-focused actions.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RISE prompt builder</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What this part does</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R - Role</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FMEA facilitator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I - Input</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Only FMEAInput; preserve four rows and supplied ratings</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S - Steps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calculate RPN; rank; flag Severity 9+; propose evidence and action</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E - Expectations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Show formula; do not invent incidents, ratings or approval</t>
   </si>
   <si>
     <t xml:space="preserve">RPN</t>
@@ -224,7 +254,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -292,6 +322,21 @@
       <family val="0"/>
       <charset val="1"/>
     </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <color rgb="FF087F8C"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF142C3E"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -347,12 +392,16 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="11">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -372,8 +421,20 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -695,85 +756,85 @@
   <dimension ref="A1:B10"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="105"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="105"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+      <c r="B1" s="2"/>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="4" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="s">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="s">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="4" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2" t="s">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="4" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2" t="s">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="4" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2" t="s">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="4" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="2" t="s">
+    <row r="8" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="4" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="2" t="s">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="4" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="2" t="s">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="4" t="s">
         <v>18</v>
       </c>
     </row>
@@ -799,159 +860,159 @@
   <dimension ref="A1:I5"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="27"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="27"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="11"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="4" t="s">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="H1" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="I1" s="5" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="5" t="s">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="F2" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="G2" s="5" t="n">
+      <c r="G2" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="H2" s="5" t="n">
+      <c r="H2" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="I2" s="5" t="n">
+      <c r="I2" s="6" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="5" t="s">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="F3" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="G3" s="5" t="n">
+      <c r="G3" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="H3" s="5" t="n">
+      <c r="H3" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="I3" s="5" t="n">
+      <c r="I3" s="6" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="5" t="s">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="E4" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="F4" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="G4" s="5" t="n">
+      <c r="G4" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="H4" s="5" t="n">
+      <c r="H4" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="I4" s="5" t="n">
+      <c r="I4" s="6" t="n">
         <v>5</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="5" t="s">
+    <row r="5" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D5" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="E5" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="F5" s="5" t="s">
+      <c r="F5" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="G5" s="5" t="n">
+      <c r="G5" s="6" t="n">
         <v>9</v>
       </c>
-      <c r="H5" s="5" t="n">
+      <c r="H5" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="I5" s="5" t="n">
+      <c r="I5" s="6" t="n">
         <v>5</v>
       </c>
     </row>
@@ -974,40 +1035,81 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="120"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="90"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="6" t="s">
+    <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="7" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="81.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="4" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="6" t="s">
+    <row r="3" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="7" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="4" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="6" t="s">
+    <row r="5" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="7" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="4" t="s">
         <v>56</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="B11" s="10" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="B12" s="10" t="s">
+        <v>66</v>
       </c>
     </row>
   </sheetData>
@@ -1029,287 +1131,287 @@
   <dimension ref="A1:N5"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="9" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="9" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="30"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="4" t="s">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="H1" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="I1" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="J1" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="K1" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="L1" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="M1" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="N1" s="4" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="5" t="str">
+      <c r="J1" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="K1" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="L1" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="M1" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="N1" s="5" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="6" t="str">
         <f aca="false">FMEA_Input!A2</f>
         <v>FM01</v>
       </c>
-      <c r="B2" s="5" t="str">
+      <c r="B2" s="6" t="str">
         <f aca="false">FMEA_Input!B2</f>
         <v>Deliver liquid</v>
       </c>
-      <c r="C2" s="5" t="str">
+      <c r="C2" s="6" t="str">
         <f aca="false">FMEA_Input!C2</f>
         <v>Low delivery</v>
       </c>
-      <c r="D2" s="5" t="str">
+      <c r="D2" s="6" t="str">
         <f aca="false">FMEA_Input!D2</f>
         <v>Incorrect dose</v>
       </c>
-      <c r="E2" s="5" t="str">
+      <c r="E2" s="6" t="str">
         <f aca="false">FMEA_Input!E2</f>
         <v>Restricted strainer</v>
       </c>
-      <c r="F2" s="5" t="str">
+      <c r="F2" s="6" t="str">
         <f aca="false">FMEA_Input!F2</f>
         <v>Delivery test</v>
       </c>
-      <c r="G2" s="5" t="n">
+      <c r="G2" s="6" t="n">
         <f aca="false">FMEA_Input!G2</f>
         <v>7</v>
       </c>
-      <c r="H2" s="5" t="n">
+      <c r="H2" s="6" t="n">
         <f aca="false">FMEA_Input!H2</f>
         <v>5</v>
       </c>
-      <c r="I2" s="5" t="n">
+      <c r="I2" s="6" t="n">
         <f aca="false">FMEA_Input!I2</f>
         <v>4</v>
       </c>
-      <c r="J2" s="5" t="n">
+      <c r="J2" s="6" t="n">
         <f aca="false">G2*H2*I2</f>
         <v>140</v>
       </c>
-      <c r="K2" s="5" t="n">
+      <c r="K2" s="6" t="n">
         <f aca="false">RANK(J2,$J$2:$J$5,0)</f>
         <v>1</v>
       </c>
-      <c r="L2" s="5" t="str">
+      <c r="L2" s="6" t="str">
         <f aca="false">IF(OR(G2&gt;=9,J2&gt;=100),"Review now","Review")</f>
         <v>Review now</v>
       </c>
-      <c r="M2" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="N2" s="5" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="5" t="str">
+      <c r="M2" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="N2" s="6" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="6" t="str">
         <f aca="false">FMEA_Input!A3</f>
         <v>FM02</v>
       </c>
-      <c r="B3" s="5" t="str">
+      <c r="B3" s="6" t="str">
         <f aca="false">FMEA_Input!B3</f>
         <v>Start pump</v>
       </c>
-      <c r="C3" s="5" t="str">
+      <c r="C3" s="6" t="str">
         <f aca="false">FMEA_Input!C3</f>
         <v>Pump does not start</v>
       </c>
-      <c r="D3" s="5" t="str">
+      <c r="D3" s="6" t="str">
         <f aca="false">FMEA_Input!D3</f>
         <v>No delivery</v>
       </c>
-      <c r="E3" s="5" t="str">
+      <c r="E3" s="6" t="str">
         <f aca="false">FMEA_Input!E3</f>
         <v>Power interruption</v>
       </c>
-      <c r="F3" s="5" t="str">
+      <c r="F3" s="6" t="str">
         <f aca="false">FMEA_Input!F3</f>
         <v>Start check</v>
       </c>
-      <c r="G3" s="5" t="n">
+      <c r="G3" s="6" t="n">
         <f aca="false">FMEA_Input!G3</f>
         <v>8</v>
       </c>
-      <c r="H3" s="5" t="n">
+      <c r="H3" s="6" t="n">
         <f aca="false">FMEA_Input!H3</f>
         <v>3</v>
       </c>
-      <c r="I3" s="5" t="n">
+      <c r="I3" s="6" t="n">
         <f aca="false">FMEA_Input!I3</f>
         <v>3</v>
       </c>
-      <c r="J3" s="5" t="n">
+      <c r="J3" s="6" t="n">
         <f aca="false">G3*H3*I3</f>
         <v>72</v>
       </c>
-      <c r="K3" s="5" t="n">
+      <c r="K3" s="6" t="n">
         <f aca="false">RANK(J3,$J$2:$J$5,0)</f>
         <v>4</v>
       </c>
-      <c r="L3" s="5" t="str">
+      <c r="L3" s="6" t="str">
         <f aca="false">IF(OR(G3&gt;=9,J3&gt;=100),"Review now","Review")</f>
         <v>Review</v>
       </c>
-      <c r="M3" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="N3" s="5" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="5" t="str">
+      <c r="M3" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="N3" s="6" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="6" t="str">
         <f aca="false">FMEA_Input!A4</f>
         <v>FM03</v>
       </c>
-      <c r="B4" s="5" t="str">
+      <c r="B4" s="6" t="str">
         <f aca="false">FMEA_Input!B4</f>
         <v>Measure flow</v>
       </c>
-      <c r="C4" s="5" t="str">
+      <c r="C4" s="6" t="str">
         <f aca="false">FMEA_Input!C4</f>
         <v>Incorrect flow reading</v>
       </c>
-      <c r="D4" s="5" t="str">
+      <c r="D4" s="6" t="str">
         <f aca="false">FMEA_Input!D4</f>
         <v>Wrong adjustment</v>
       </c>
-      <c r="E4" s="5" t="str">
+      <c r="E4" s="6" t="str">
         <f aca="false">FMEA_Input!E4</f>
         <v>Sensor drift</v>
       </c>
-      <c r="F4" s="5" t="str">
+      <c r="F4" s="6" t="str">
         <f aca="false">FMEA_Input!F4</f>
         <v>Calibration check</v>
       </c>
-      <c r="G4" s="5" t="n">
+      <c r="G4" s="6" t="n">
         <f aca="false">FMEA_Input!G4</f>
         <v>6</v>
       </c>
-      <c r="H4" s="5" t="n">
+      <c r="H4" s="6" t="n">
         <f aca="false">FMEA_Input!H4</f>
         <v>4</v>
       </c>
-      <c r="I4" s="5" t="n">
+      <c r="I4" s="6" t="n">
         <f aca="false">FMEA_Input!I4</f>
         <v>5</v>
       </c>
-      <c r="J4" s="5" t="n">
+      <c r="J4" s="6" t="n">
         <f aca="false">G4*H4*I4</f>
         <v>120</v>
       </c>
-      <c r="K4" s="5" t="n">
+      <c r="K4" s="6" t="n">
         <f aca="false">RANK(J4,$J$2:$J$5,0)</f>
         <v>2</v>
       </c>
-      <c r="L4" s="5" t="str">
+      <c r="L4" s="6" t="str">
         <f aca="false">IF(OR(G4&gt;=9,J4&gt;=100),"Review now","Review")</f>
         <v>Review now</v>
       </c>
-      <c r="M4" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="N4" s="5" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="5" t="str">
+      <c r="M4" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="N4" s="6" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="6" t="str">
         <f aca="false">FMEA_Input!A5</f>
         <v>FM04</v>
       </c>
-      <c r="B5" s="5" t="str">
+      <c r="B5" s="6" t="str">
         <f aca="false">FMEA_Input!B5</f>
         <v>Contain liquid</v>
       </c>
-      <c r="C5" s="5" t="str">
+      <c r="C5" s="6" t="str">
         <f aca="false">FMEA_Input!C5</f>
         <v>Connection leaks</v>
       </c>
-      <c r="D5" s="5" t="str">
+      <c r="D5" s="6" t="str">
         <f aca="false">FMEA_Input!D5</f>
         <v>Exposure and loss of containment</v>
       </c>
-      <c r="E5" s="5" t="str">
+      <c r="E5" s="6" t="str">
         <f aca="false">FMEA_Input!E5</f>
         <v>Loose fitting</v>
       </c>
-      <c r="F5" s="5" t="str">
+      <c r="F5" s="6" t="str">
         <f aca="false">FMEA_Input!F5</f>
         <v>Visual inspection</v>
       </c>
-      <c r="G5" s="5" t="n">
+      <c r="G5" s="6" t="n">
         <f aca="false">FMEA_Input!G5</f>
         <v>9</v>
       </c>
-      <c r="H5" s="5" t="n">
+      <c r="H5" s="6" t="n">
         <f aca="false">FMEA_Input!H5</f>
         <v>2</v>
       </c>
-      <c r="I5" s="5" t="n">
+      <c r="I5" s="6" t="n">
         <f aca="false">FMEA_Input!I5</f>
         <v>5</v>
       </c>
-      <c r="J5" s="5" t="n">
+      <c r="J5" s="6" t="n">
         <f aca="false">G5*H5*I5</f>
         <v>90</v>
       </c>
-      <c r="K5" s="5" t="n">
+      <c r="K5" s="6" t="n">
         <f aca="false">RANK(J5,$J$2:$J$5,0)</f>
         <v>3</v>
       </c>
-      <c r="L5" s="5" t="str">
+      <c r="L5" s="6" t="str">
         <f aca="false">IF(OR(G5&gt;=9,J5&gt;=100),"Review now","Review")</f>
         <v>Review now</v>
       </c>
-      <c r="M5" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="N5" s="5" t="s">
-        <v>63</v>
+      <c r="M5" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="N5" s="6" t="s">
+        <v>73</v>
       </c>
     </row>
   </sheetData>
